--- a/data/trans_dic/P7_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P7_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con salud general regular o mala</t>
+          <t>Población con salud general regular o mala (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,51; 15,15</t>
+          <t>8,73; 14,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 14,14</t>
+          <t>7,71; 14,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,65</t>
+          <t>5,59; 10,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,52; 17,25</t>
+          <t>10,71; 17,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,79; 21,28</t>
+          <t>12,71; 20,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,92</t>
+          <t>6,71; 13,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,81; 13,45</t>
+          <t>6,93; 14,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 16,37</t>
+          <t>11,26; 16,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,08; 16,15</t>
+          <t>11,36; 16,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,03; 12,72</t>
+          <t>8,13; 12,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 10,95</t>
+          <t>6,8; 10,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,67; 15,74</t>
+          <t>11,57; 15,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,91; 14,87</t>
+          <t>8,1; 15,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,97; 14,23</t>
+          <t>8,14; 14,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 14,67</t>
+          <t>8,35; 15,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 15,38</t>
+          <t>9,74; 15,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,16; 19,64</t>
+          <t>12,0; 19,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,51; 18,12</t>
+          <t>10,36; 18,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,01; 17,36</t>
+          <t>10,17; 17,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,49; 16,88</t>
+          <t>11,53; 17,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,84; 15,77</t>
+          <t>10,72; 15,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 15,16</t>
+          <t>9,93; 14,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 14,85</t>
+          <t>9,88; 14,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,08; 15,1</t>
+          <t>11,29; 15,4</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,51; 19,63</t>
+          <t>13,31; 19,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,97; 25,97</t>
+          <t>19,03; 25,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,26; 20,97</t>
+          <t>14,48; 21,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 22,39</t>
+          <t>5,47; 22,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,15; 35,35</t>
+          <t>21,67; 35,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,64; 29,67</t>
+          <t>18,98; 30,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,85; 36,19</t>
+          <t>20,24; 35,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,1; 34,69</t>
+          <t>23,3; 34,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,12; 21,92</t>
+          <t>16,16; 22,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,28; 25,88</t>
+          <t>20,04; 25,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,11; 23,26</t>
+          <t>16,72; 23,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 24,29</t>
+          <t>7,68; 24,2</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,95; 21,52</t>
+          <t>16,96; 21,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,56; 22,66</t>
+          <t>17,55; 22,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,12; 21,69</t>
+          <t>17,05; 21,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,45; 24,66</t>
+          <t>19,62; 25,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,21; 27,44</t>
+          <t>21,31; 27,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,76; 24,87</t>
+          <t>18,6; 24,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,4; 22,88</t>
+          <t>17,01; 22,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 21,56</t>
+          <t>9,5; 21,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,38; 22,99</t>
+          <t>19,25; 22,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,81; 22,62</t>
+          <t>18,76; 22,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,69; 21,34</t>
+          <t>17,67; 21,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,13; 22,14</t>
+          <t>12,95; 22,07</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,82; 28,32</t>
+          <t>18,86; 28,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,27; 22,14</t>
+          <t>15,08; 22,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,43; 25,33</t>
+          <t>18,68; 25,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,3; 27,68</t>
+          <t>19,17; 27,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,07; 37,08</t>
+          <t>29,41; 37,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,0; 40,03</t>
+          <t>32,66; 39,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,04; 35,34</t>
+          <t>28,11; 35,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,59; 34,83</t>
+          <t>23,26; 34,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,17; 32,18</t>
+          <t>26,17; 32,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,52; 31,78</t>
+          <t>26,66; 31,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,46; 29,61</t>
+          <t>24,75; 29,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,64; 30,4</t>
+          <t>21,98; 30,38</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,59</t>
+          <t>2,16; 7,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 8,36</t>
+          <t>2,73; 9,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,67</t>
+          <t>1,44; 5,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,5</t>
+          <t>1,62; 6,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,24; 38,69</t>
+          <t>33,35; 38,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,85; 35,58</t>
+          <t>29,68; 35,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,96; 31,84</t>
+          <t>26,18; 32,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27,66; 33,46</t>
+          <t>27,46; 33,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,57; 32,36</t>
+          <t>27,46; 32,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,02; 30,02</t>
+          <t>24,92; 29,85</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,24; 26,23</t>
+          <t>21,05; 26,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,43; 26,11</t>
+          <t>21,33; 26,4</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,33; 16,95</t>
+          <t>14,43; 16,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,45; 18,09</t>
+          <t>15,36; 18,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,45; 17,1</t>
+          <t>14,49; 16,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,65; 18,43</t>
+          <t>13,14; 18,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,2; 30,32</t>
+          <t>27,03; 30,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,17; 28,1</t>
+          <t>25,17; 28,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,42; 25,46</t>
+          <t>22,32; 25,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,02; 24,58</t>
+          <t>18,21; 24,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,25; 23,38</t>
+          <t>21,13; 23,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,78; 22,79</t>
+          <t>20,86; 22,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,88</t>
+          <t>18,88; 20,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,21; 21,31</t>
+          <t>17,1; 21,17</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con salud general regular o mala</t>
+          <t>Población con salud general regular o mala (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40312; 71772</t>
+          <t>41338; 70238</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34376; 61538</t>
+          <t>33572; 61981</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23264; 45377</t>
+          <t>23802; 46551</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53138; 87155</t>
+          <t>54083; 86741</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39210; 65258</t>
+          <t>38987; 63511</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21398; 43777</t>
+          <t>21092; 43976</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23621; 46674</t>
+          <t>24040; 48807</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50019; 73262</t>
+          <t>50382; 72548</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>86471; 126026</t>
+          <t>88694; 125872</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60212; 95391</t>
+          <t>60943; 95790</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51821; 84643</t>
+          <t>52577; 84387</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>111158; 149911</t>
+          <t>110201; 150861</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28932; 54391</t>
+          <t>29647; 55165</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33398; 59607</t>
+          <t>34076; 62235</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31637; 55204</t>
+          <t>31423; 57724</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43533; 69562</t>
+          <t>44035; 70242</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45217; 73028</t>
+          <t>44632; 72519</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35427; 61058</t>
+          <t>34901; 62905</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37246; 64616</t>
+          <t>37860; 66104</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43948; 64576</t>
+          <t>44122; 66203</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79943; 116318</t>
+          <t>79090; 115085</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75189; 114620</t>
+          <t>75050; 112571</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74796; 111164</t>
+          <t>73986; 111661</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92525; 126065</t>
+          <t>94225; 128567</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>73291; 106498</t>
+          <t>72178; 106553</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>118840; 162670</t>
+          <t>119224; 162706</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74406; 109469</t>
+          <t>75558; 110329</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33333; 149651</t>
+          <t>36522; 150349</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35482; 59313</t>
+          <t>36354; 59822</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48490; 77173</t>
+          <t>49370; 78764</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34199; 59359</t>
+          <t>33196; 58016</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38564; 57896</t>
+          <t>38883; 57601</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>114463; 155660</t>
+          <t>114760; 156430</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179740; 229415</t>
+          <t>177635; 229179</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117361; 159560</t>
+          <t>114708; 158574</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54772; 202852</t>
+          <t>64126; 202124</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>209853; 266449</t>
+          <t>209967; 265006</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>203280; 262309</t>
+          <t>203162; 259606</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>196863; 249355</t>
+          <t>195988; 248482</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>201240; 255196</t>
+          <t>202993; 259342</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>151484; 196020</t>
+          <t>152240; 198251</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>143847; 190691</t>
+          <t>142565; 188336</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>143723; 188939</t>
+          <t>140523; 187717</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82790; 210866</t>
+          <t>92885; 210660</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>378514; 448962</t>
+          <t>375866; 448183</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>361968; 435348</t>
+          <t>360930; 434555</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349508; 421648</t>
+          <t>348992; 419480</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>284429; 445563</t>
+          <t>260757; 444226</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>65980; 99267</t>
+          <t>66124; 98710</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77871; 112899</t>
+          <t>76901; 112615</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114379; 157217</t>
+          <t>115922; 155786</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91667; 131485</t>
+          <t>91057; 128298</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>165316; 210879</t>
+          <t>167266; 212546</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>250337; 303655</t>
+          <t>247732; 302932</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>206406; 260171</t>
+          <t>206954; 259269</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>190080; 293069</t>
+          <t>195728; 293962</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>240599; 295865</t>
+          <t>240577; 296746</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>336396; 403059</t>
+          <t>338177; 400948</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>331858; 401701</t>
+          <t>335826; 400633</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>298036; 400225</t>
+          <t>289351; 399858</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6307; 19666</t>
+          <t>6451; 20946</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6812; 22315</t>
+          <t>7274; 24329</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4821; 16234</t>
+          <t>4108; 16767</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3766; 13219</t>
+          <t>3899; 14804</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>415127; 483187</t>
+          <t>416506; 481845</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>330886; 394351</t>
+          <t>328932; 394854</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>280591; 344197</t>
+          <t>283004; 346947</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>210581; 254775</t>
+          <t>209045; 253232</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>426437; 500594</t>
+          <t>424832; 497201</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>344071; 412794</t>
+          <t>342662; 410568</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>290358; 358560</t>
+          <t>287777; 356050</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>214734; 261605</t>
+          <t>213671; 264463</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>468504; 553987</t>
+          <t>471782; 551287</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>527645; 617805</t>
+          <t>524581; 616095</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>488636; 578067</t>
+          <t>490052; 574061</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>426965; 622163</t>
+          <t>443644; 620902</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>918711; 1024115</t>
+          <t>913069; 1021443</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>892471; 996086</t>
+          <t>892433; 1003009</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>790591; 897785</t>
+          <t>787209; 891271</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>644545; 879464</t>
+          <t>651665; 879220</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1412485; 1554047</t>
+          <t>1404406; 1541995</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1446259; 1586247</t>
+          <t>1451544; 1583470</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1298096; 1442158</t>
+          <t>1304289; 1438175</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1196778; 1481764</t>
+          <t>1188842; 1472197</t>
         </is>
       </c>
     </row>
